--- a/docs/PROJECT_EFFORT_TRACKER.xlsx
+++ b/docs/PROJECT_EFFORT_TRACKER.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Project Effort Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Effort Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -111,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -125,11 +125,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -171,6 +199,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -568,7 +598,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Last Updated: February 12, 2026 11:10 AM</t>
+          <t>Last Updated: February 27, 2026</t>
         </is>
       </c>
     </row>
@@ -1036,124 +1066,163 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>SQLite to MySQL migration (18 tables, 6032 rows).
+Migration script + DB-agnostic migration files.
+Test infrastructure fix (conftest.py get_db import).
+Comprehensive E2E testing (59/59 backend tests).
+11 browser modules verified via Playwright.
+Test report documentation (228 lines).</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>12 modified/created</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>MySQL migration + full testing session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="12">
-        <f>SUM(F6:F13)</f>
+      <c r="F15">
+        <f>SUM(F6:F14)</f>
         <v/>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Note: Sessions 1-7 hours are estimated from git commit timestamps and file activity. Session 8 onward will be tracked with actual start/end times.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Project Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Project Start:</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>January 18, 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Technology Stack:</t>
+          <t>Project Start:</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>FastAPI (Python) + Next.js 14 (TypeScript) + SQLite</t>
+          <t>January 18, 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Total Sessions:</t>
+          <t>Technology Stack:</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>FastAPI (Python) + Next.js 14 (TypeScript) + MySQL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Total Hours:</t>
+          <t>Total Sessions:</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>~151.5 (Sessions 1-7 estimated, Session 8+ actual)</t>
+          <t>FastAPI (Python) + Next.js 14 (TypeScript) + MySQL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Key Modules:</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Lead Sourcing, Contact Enrichment, Email Validation, Outreach, Warmup Engine, AI Content</t>
-        </is>
+          <t>Total Hours:</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>Key Modules:</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>~159.5 (Sessions 1-7 estimated, Session 8+ actual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>Deployed Tools:</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Claude Code (AI pair programming)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B18:J18"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
